--- a/artfynd/A 14771-2022 artfynd.xlsx
+++ b/artfynd/A 14771-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14771-2022 artfynd.xlsx
+++ b/artfynd/A 14771-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73910126</v>
+        <v>73910138</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646045.9097672219</v>
+        <v>645962</v>
       </c>
       <c r="R2" t="n">
-        <v>6569575.780726393</v>
+        <v>6569437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73910163</v>
+        <v>73910127</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646005.8850177077</v>
+        <v>646090</v>
       </c>
       <c r="R3" t="n">
-        <v>6569495.88833645</v>
+        <v>6569580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-07-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sigg</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73910138</v>
+        <v>73910163</v>
       </c>
       <c r="B4" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645961.9796854596</v>
+        <v>646006</v>
       </c>
       <c r="R4" t="n">
-        <v>6569436.843412766</v>
+        <v>6569496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +934,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +964,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Lisa Sigg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73910164</v>
+        <v>73910126</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646044.9217345737</v>
+        <v>646046</v>
       </c>
       <c r="R5" t="n">
-        <v>6569548.088339362</v>
+        <v>6569576</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,22 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-07-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-07-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1061,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Sigg</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73910127</v>
+        <v>73910164</v>
       </c>
       <c r="B6" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646089.8661547067</v>
+        <v>646045</v>
       </c>
       <c r="R6" t="n">
-        <v>6569580.030564732</v>
+        <v>6569548</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1158,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Lisa Sigg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 14771-2022 artfynd.xlsx
+++ b/artfynd/A 14771-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910127</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>